--- a/review/etnografiya/may-december/august/august.xlsx
+++ b/review/etnografiya/may-december/august/august.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему изогнутое лезвие удобно для выбранного движения?</t>
+          <t xml:space="preserve">Серп работает с горстью стеблей, удержанной рукой. Жатва складывается из множества повторённых движений — урожай собирают в человеческом масштабе.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарный день связывали с переменами погоды?</t>
+          <t xml:space="preserve">Ильин день входит в народный рассказ о перемене лета. Календарная память соединяет праздник с сезонными наблюдениями, не превращая их в прогноз.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как охапка стеблей превращается в удобный груз?</t>
+          <t xml:space="preserve">Сноп придаёт срезанным стеблям переносную форму. Урожай становится отдельной связкой, которую можно поднять, поставить и перевезти.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли связать стебли без покупной верёвки?</t>
+          <t xml:space="preserve">Перевясло делают из самого растительного материала. Часть урожая удерживает другую часть — простое крепление рождается прямо во время работы.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем наряд для работы отличается от праздничного?</t>
+          <t xml:space="preserve">Жнивная рубаха принадлежит тяжёлой поре полевых работ. Крой и материал помогают увидеть связь одежды с движением и сезонной нагрузкой.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто присматривает за младшими, пока взрослые жнут?</t>
+          <t xml:space="preserve">В семейной работе на поле было несколько ролей. Детское участие требует увидеть конкретное занятие, а не переносить взрослый труд на всех одинаково.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему завершение жатвы не всегда означает пустое поле?</t>
+          <t xml:space="preserve">Последние колосья могли оставлять для обрядового действия. Завершение жатвы получало местный смысл, который не сводится к уборке остатка урожая.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему орудие состоит из двух подвижных частей?</t>
+          <t xml:space="preserve">Цеп отделяет зерно ударами по снопам. Подвижное соединение деревянных частей превращает замах человека в работу другого конца орудия.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем снопы везут в особое место?</t>
+          <t xml:space="preserve">Ток — отдельная площадка для работы с урожаем. Расположение снопов и действий показывает, что обмолоту нужен организованный простор.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делает отдельная постройка, чего не сделает жилая изба?</t>
+          <t xml:space="preserve">В овине снопы готовят к обмолоту. Урожай проходит дополнительный этап обработки, прежде чем зерно отделят от стеблей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как движение воздуха отделяет лёгкое от тяжёлого?</t>
+          <t xml:space="preserve">Воздух помогает отделить зерно от лёгких примесей. Веялка использует различие материала — невидимый поток становится рабочей силой.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему зерно нельзя просто высыпать где угодно?</t>
+          <t xml:space="preserve">В сусеке зерну отводят отдельное место. Домашний запас требует границ и порядка, чтобы результат одного сезона служил семье дальше.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает увеличенная ячейка о собранном продукте?</t>
+          <t xml:space="preserve">Медовый сот приносит природную структуру в хозяйство человека. Пасечный труд начинается с внимания к тому, что создают сами пчёлы.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как хозяйственный запас входит в календарный обычай?</t>
+          <t xml:space="preserve">На Медовый Спас продукт пасеки становится праздничным даром. Работа с пчёлами входит в годовой круг встреч, угощения и благодарности.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся ценным после извлечения мёда?</t>
+          <t xml:space="preserve">Пасека даёт не только мёд, но и воск. Один хозяйственный мир снабжает человека разными материалами, каждому из которых находится своё применение.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плод становится зимним запасом?</t>
+          <t xml:space="preserve">Мочёные яблоки меняют вкус во время хранения. Заготовка превращает летний плод в другой опыт домашней еды, доступный после сбора урожая.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему после сушки меняются размер и способ хранения?</t>
+          <t xml:space="preserve">При сушке грибы становятся легче и занимают меньше места. Лесной сбор получает форму запаса — результат сохраняют отдельной домашней работой.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему для ягод важны форма и глубина корзины?</t>
+          <t xml:space="preserve">Ягодное лукошко должно донести хрупкий сбор. Плетёная форма рассчитана на содержимое: труд собирателя продолжается дорогой домой.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает яблоко, семейный стол и церковный календарь?</t>
+          <t xml:space="preserve">Яблочный Спас связывает плоды с праздничной историей. Сезонный урожай появляется в угощении и обычае конкретного местного сообщества.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всегда ли кисель был сладким напитком?</t>
+          <t xml:space="preserve">Знакомое слово «кисель» хранит историю другого блюда. Сравнение старого и нового стола показывает, как название переживает перемены приготовления.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем готовая мука отличается от просто размолотого зерна?</t>
+          <t xml:space="preserve">Толокно — результат нескольких этапов подготовки зерна. За простой домашней пищей скрыто время работы, которого не видно в готовой порции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем рассматривать посуду сбоку, а не только спереди?</t>
+          <t xml:space="preserve">Просвет в кваснике делает сосуд узнаваемым. Необычная форма предлагает рассмотреть устройство бытовой вещи со всех сторон, а не только спереди.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как напиток переносили и разливали покупателям?</t>
+          <t xml:space="preserve">Сбитенник связан с горячим напитком и уличным угощением. Специальный сосуд выводит домашнее тепло в пространство городской встречи.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у одной семьи бывают разные правила трапезы?</t>
+          <t xml:space="preserve">Постный и скоромный стол различаются набором продуктов. Годовой календарь меняет повседневный выбор еды, не меняя саму потребность накормить семью.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как положить заготовку туда, куда рукой не достать?</t>
+          <t xml:space="preserve">Длинная хлебная лопата достигает глубины печи. Расстояние между руками и жаром превращено в размер простого деревянного инструмента.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему богатый запас всё равно делят?</t>
+          <t xml:space="preserve">Часть зерна оставляют для нового посева. Урожай одновременно кормит сегодня и сохраняет возможность следующего года — весь запас съесть нельзя.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему путь к ткани проходит через воду?</t>
+          <t xml:space="preserve">Лён меняется на мочиле ещё до прядения. Будущая нить начинается с обработки стебля, когда ткань пока невозможно увидеть в материале.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник соседствует с заботой об урожае?</t>
+          <t xml:space="preserve">Успение входит в народную память о завершении лета. Праздник встречается с хозяйственным сезоном, но местный порядок работ требует отдельного рассказа.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему один день называется разными дарами?</t>
+          <t xml:space="preserve">Ореховый, Хлебный и Холщовый — имена одного Спаса. Разные названия сохраняют несколько хозяйственных связей внутри общей праздничной даты.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда уходит стебель после обмолота?</t>
+          <t xml:space="preserve">Солома служит подстилкой после того, как зерно убрано. У урожая оказывается больше одной полезной части — хозяйство продолжает использовать растение.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочему животному посвящали особый день?</t>
+          <t xml:space="preserve">День Флора и Лавра связан с заботой о лошадях. Праздничное внимание обращено к животному, чья сила участвовала в ежедневном человеческом труде.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
